--- a/MAIN/Trade Studies/Trade Study Test Matrix Jet Flying Wing.xlsx
+++ b/MAIN/Trade Studies/Trade Study Test Matrix Jet Flying Wing.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\ASEN_Aircraft_Design\MAIN\Trade Studies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C2055F-8C12-46D1-A58E-C146D0A62D1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5670FF89-255A-471E-9C03-171C4C4AEBC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="11520" windowHeight="12360" xr2:uid="{8F92E0EF-7E82-4DBA-A0D5-7EFE37AE0789}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{8F92E0EF-7E82-4DBA-A0D5-7EFE37AE0789}"/>
   </bookViews>
   <sheets>
     <sheet name="Sref &amp; AR 1" sheetId="16" r:id="rId1"/>
@@ -163,7 +163,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="205" uniqueCount="79">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="225" uniqueCount="83">
   <si>
     <t>Re</t>
   </si>
@@ -400,6 +400,18 @@
   </si>
   <si>
     <t>Varies</t>
+  </si>
+  <si>
+    <t>Fail</t>
+  </si>
+  <si>
+    <t>Pass slim margin</t>
+  </si>
+  <si>
+    <t>Pass medium margin</t>
+  </si>
+  <si>
+    <t>Pass high margin</t>
   </si>
 </sst>
 </file>
@@ -1474,7 +1486,9 @@
       </c>
       <c r="H40" s="28"/>
       <c r="I40" s="28"/>
-      <c r="J40" s="28"/>
+      <c r="J40" s="28" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A41" s="6">
@@ -1500,7 +1514,9 @@
       </c>
       <c r="H41" s="28"/>
       <c r="I41" s="28"/>
-      <c r="J41" s="28"/>
+      <c r="J41" s="28" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A42" s="6">
@@ -1526,7 +1542,9 @@
       </c>
       <c r="H42" s="28"/>
       <c r="I42" s="28"/>
-      <c r="J42" s="28"/>
+      <c r="J42" s="28" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A43" s="6">
@@ -1552,7 +1570,9 @@
       </c>
       <c r="H43" s="28"/>
       <c r="I43" s="28"/>
-      <c r="J43" s="28"/>
+      <c r="J43" s="28" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A44" s="6">
@@ -1578,7 +1598,9 @@
       </c>
       <c r="H44" s="28"/>
       <c r="I44" s="28"/>
-      <c r="J44" s="28"/>
+      <c r="J44" s="28" t="s">
+        <v>79</v>
+      </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A45" s="29">
@@ -1604,7 +1626,9 @@
       </c>
       <c r="H45" s="28"/>
       <c r="I45" s="28"/>
-      <c r="J45" s="28"/>
+      <c r="J45" s="28" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A46" s="29">
@@ -1630,7 +1654,9 @@
       </c>
       <c r="H46" s="28"/>
       <c r="I46" s="28"/>
-      <c r="J46" s="28"/>
+      <c r="J46" s="28" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A47" s="29">
@@ -1656,7 +1682,9 @@
       </c>
       <c r="H47" s="28"/>
       <c r="I47" s="28"/>
-      <c r="J47" s="28"/>
+      <c r="J47" s="28" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A48" s="29">
@@ -1682,7 +1710,9 @@
       </c>
       <c r="H48" s="28"/>
       <c r="I48" s="28"/>
-      <c r="J48" s="28"/>
+      <c r="J48" s="28" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49" s="29">
@@ -1708,7 +1738,9 @@
       </c>
       <c r="H49" s="28"/>
       <c r="I49" s="28"/>
-      <c r="J49" s="28"/>
+      <c r="J49" s="28" t="s">
+        <v>80</v>
+      </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50" s="29">
@@ -1734,7 +1766,9 @@
       </c>
       <c r="H50" s="28"/>
       <c r="I50" s="28"/>
-      <c r="J50" s="28"/>
+      <c r="J50" s="28" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51" s="29">
@@ -1760,7 +1794,9 @@
       </c>
       <c r="H51" s="28"/>
       <c r="I51" s="28"/>
-      <c r="J51" s="28"/>
+      <c r="J51" s="28" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52" s="6">
@@ -1786,7 +1822,9 @@
       </c>
       <c r="H52" s="28"/>
       <c r="I52" s="28"/>
-      <c r="J52" s="28"/>
+      <c r="J52" s="28" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53" s="6">
@@ -1812,7 +1850,9 @@
       </c>
       <c r="H53" s="28"/>
       <c r="I53" s="28"/>
-      <c r="J53" s="28"/>
+      <c r="J53" s="28" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54" s="6">
@@ -1838,7 +1878,9 @@
       </c>
       <c r="H54" s="28"/>
       <c r="I54" s="28"/>
-      <c r="J54" s="28"/>
+      <c r="J54" s="28" t="s">
+        <v>81</v>
+      </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55" s="6">
@@ -1864,7 +1906,9 @@
       </c>
       <c r="H55" s="28"/>
       <c r="I55" s="28"/>
-      <c r="J55" s="28"/>
+      <c r="J55" s="28" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56" s="6">
@@ -1890,7 +1934,9 @@
       </c>
       <c r="H56" s="28"/>
       <c r="I56" s="28"/>
-      <c r="J56" s="28"/>
+      <c r="J56" s="28" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57" s="6">
@@ -1916,7 +1962,9 @@
       </c>
       <c r="H57" s="28"/>
       <c r="I57" s="28"/>
-      <c r="J57" s="28"/>
+      <c r="J57" s="28" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58" s="6">
@@ -1942,7 +1990,9 @@
       </c>
       <c r="H58" s="28"/>
       <c r="I58" s="28"/>
-      <c r="J58" s="28"/>
+      <c r="J58" s="28" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59" s="6">
@@ -1968,7 +2018,9 @@
       </c>
       <c r="H59" s="28"/>
       <c r="I59" s="28"/>
-      <c r="J59" s="28"/>
+      <c r="J59" s="28" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60" s="6"/>

--- a/MAIN/Trade Studies/Trade Study Test Matrix Jet Flying Wing.xlsx
+++ b/MAIN/Trade Studies/Trade Study Test Matrix Jet Flying Wing.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Documents\GitHub\ASEN_Aircraft_Design\MAIN\Trade Studies\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5670FF89-255A-471E-9C03-171C4C4AEBC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92A9B827-DB88-4CE6-A6C7-4E8C160C839A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{8F92E0EF-7E82-4DBA-A0D5-7EFE37AE0789}"/>
   </bookViews>
@@ -486,7 +486,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="13">
+  <fills count="15">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -555,7 +555,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="0"/>
+        <fgColor theme="9" tint="0.39997558519241921"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -624,7 +636,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="45">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -687,10 +699,6 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -718,6 +726,22 @@
     <xf numFmtId="0" fontId="2" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1051,12 +1075,12 @@
       </c>
     </row>
     <row r="3" spans="1:6" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
       <c r="E3" s="25"/>
     </row>
     <row r="4" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -1260,12 +1284,12 @@
       <c r="B19" s="11"/>
     </row>
     <row r="21" spans="1:5" s="5" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
       <c r="E21" s="26"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -1366,10 +1390,10 @@
       </c>
     </row>
     <row r="32" spans="1:5" s="10" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A32" s="32" t="s">
+      <c r="A32" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="32"/>
+      <c r="B32" s="30"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -1396,18 +1420,18 @@
       </c>
     </row>
     <row r="37" spans="1:11" s="9" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A37" s="33" t="s">
+      <c r="A37" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="33"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
     </row>
     <row r="38" spans="1:11" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>
@@ -1417,17 +1441,17 @@
       <c r="C38" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="34" t="s">
+      <c r="D38" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="E38" s="35"/>
-      <c r="F38" s="36" t="s">
+      <c r="E38" s="33"/>
+      <c r="F38" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="G38" s="37"/>
-      <c r="H38" s="37"/>
-      <c r="I38" s="37"/>
-      <c r="J38" s="38"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="35"/>
+      <c r="J38" s="36"/>
       <c r="K38" s="2"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
@@ -1463,562 +1487,562 @@
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A40" s="6">
+      <c r="A40" s="43">
         <v>1.1000000000000001</v>
       </c>
-      <c r="B40" s="29">
+      <c r="B40" s="43">
         <v>650</v>
       </c>
-      <c r="C40" s="29">
+      <c r="C40" s="43">
         <v>1.25</v>
       </c>
-      <c r="D40" s="7">
+      <c r="D40" s="44">
         <v>16333.834298527188</v>
       </c>
-      <c r="E40" s="7">
+      <c r="E40" s="44">
         <v>3829.6068257748648</v>
       </c>
-      <c r="F40" s="7">
+      <c r="F40" s="44">
         <v>25.244349266903075</v>
       </c>
-      <c r="G40" s="7">
+      <c r="G40" s="44">
         <v>0.74350226146801124</v>
       </c>
-      <c r="H40" s="28"/>
-      <c r="I40" s="28"/>
-      <c r="J40" s="28" t="s">
+      <c r="H40" s="44"/>
+      <c r="I40" s="44"/>
+      <c r="J40" s="44" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A41" s="6">
+      <c r="A41" s="43">
         <v>1.2</v>
       </c>
-      <c r="B41" s="29">
+      <c r="B41" s="43">
         <v>600</v>
       </c>
-      <c r="C41" s="29">
+      <c r="C41" s="43">
         <v>1.25</v>
       </c>
-      <c r="D41" s="7">
+      <c r="D41" s="44">
         <v>15840.810534654349</v>
       </c>
-      <c r="E41" s="7">
+      <c r="E41" s="44">
         <v>3735.9138203939165</v>
       </c>
-      <c r="F41" s="7">
+      <c r="F41" s="44">
         <v>26.519627535345688</v>
       </c>
-      <c r="G41" s="7">
+      <c r="G41" s="44">
         <v>0.76672771162539199</v>
       </c>
-      <c r="H41" s="28"/>
-      <c r="I41" s="28"/>
-      <c r="J41" s="28" t="s">
+      <c r="H41" s="44"/>
+      <c r="I41" s="44"/>
+      <c r="J41" s="44" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A42" s="6">
+      <c r="A42" s="43">
         <v>1.3</v>
       </c>
-      <c r="B42" s="29">
+      <c r="B42" s="43">
         <v>550</v>
       </c>
-      <c r="C42" s="29">
+      <c r="C42" s="43">
         <v>1.25</v>
       </c>
-      <c r="D42" s="7">
+      <c r="D42" s="44">
         <v>15358.4450762222</v>
       </c>
-      <c r="E42" s="7">
+      <c r="E42" s="44">
         <v>3656.2161254577586</v>
       </c>
-      <c r="F42" s="7">
+      <c r="F42" s="44">
         <v>28.055083312746156</v>
       </c>
-      <c r="G42" s="7">
+      <c r="G42" s="44">
         <v>0.79065237249680176</v>
       </c>
-      <c r="H42" s="28"/>
-      <c r="I42" s="28"/>
-      <c r="J42" s="28" t="s">
+      <c r="H42" s="44"/>
+      <c r="I42" s="44"/>
+      <c r="J42" s="44" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A43" s="6">
+      <c r="A43" s="43">
         <v>1.4</v>
       </c>
-      <c r="B43" s="29">
+      <c r="B43" s="43">
         <v>500</v>
       </c>
-      <c r="C43" s="29">
+      <c r="C43" s="43">
         <v>1.25</v>
       </c>
-      <c r="D43" s="7">
+      <c r="D43" s="44">
         <v>14876.85127380343</v>
       </c>
-      <c r="E43" s="7">
+      <c r="E43" s="44">
         <v>3588.3445214604499</v>
       </c>
-      <c r="F43" s="7">
+      <c r="F43" s="44">
         <v>29.894612790159044</v>
       </c>
-      <c r="G43" s="7">
+      <c r="G43" s="44">
         <v>0.81620057002485058</v>
       </c>
-      <c r="H43" s="28"/>
-      <c r="I43" s="28"/>
-      <c r="J43" s="28" t="s">
+      <c r="H43" s="44"/>
+      <c r="I43" s="44"/>
+      <c r="J43" s="44" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A44" s="6">
+      <c r="A44" s="43">
         <v>1.5</v>
       </c>
-      <c r="B44" s="29">
+      <c r="B44" s="43">
         <v>450</v>
       </c>
-      <c r="C44" s="29">
+      <c r="C44" s="43">
         <v>1.25</v>
       </c>
-      <c r="D44" s="7">
+      <c r="D44" s="44">
         <v>14413.314735081396</v>
       </c>
-      <c r="E44" s="7">
+      <c r="E44" s="44">
         <v>3543.9504951447898</v>
       </c>
-      <c r="F44" s="7">
+      <c r="F44" s="44">
         <v>32.187041144406884</v>
       </c>
-      <c r="G44" s="7">
+      <c r="G44" s="44">
         <v>0.84229895470905014</v>
       </c>
-      <c r="H44" s="28"/>
-      <c r="I44" s="28"/>
-      <c r="J44" s="28" t="s">
+      <c r="H44" s="44"/>
+      <c r="I44" s="44"/>
+      <c r="J44" s="44" t="s">
         <v>79</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A45" s="29">
+      <c r="A45" s="41">
         <v>2.1</v>
       </c>
-      <c r="B45" s="29">
+      <c r="B45" s="41">
         <v>650</v>
       </c>
-      <c r="C45" s="29">
+      <c r="C45" s="41">
         <v>1.5</v>
       </c>
-      <c r="D45" s="7">
+      <c r="D45" s="42">
         <v>16647.074847609103</v>
       </c>
-      <c r="E45" s="7">
+      <c r="E45" s="42">
         <v>3589.7699248129902</v>
       </c>
-      <c r="F45" s="7">
+      <c r="F45" s="42">
         <v>25.730229049079611</v>
       </c>
-      <c r="G45" s="7">
+      <c r="G45" s="42">
         <v>0.72946224976967933</v>
       </c>
-      <c r="H45" s="28"/>
-      <c r="I45" s="28"/>
-      <c r="J45" s="28" t="s">
+      <c r="H45" s="42"/>
+      <c r="I45" s="42"/>
+      <c r="J45" s="42" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A46" s="29">
+      <c r="A46" s="41">
         <v>2.2000000000000002</v>
       </c>
-      <c r="B46" s="29">
+      <c r="B46" s="41">
         <v>600</v>
       </c>
-      <c r="C46" s="29">
+      <c r="C46" s="41">
         <v>1.5</v>
       </c>
-      <c r="D46" s="7">
+      <c r="D46" s="42">
         <v>16087.625962990722</v>
       </c>
-      <c r="E46" s="7">
+      <c r="E46" s="42">
         <v>3471.7945290275702</v>
       </c>
-      <c r="F46" s="7">
+      <c r="F46" s="42">
         <v>26.931524495060259</v>
       </c>
-      <c r="G46" s="7">
+      <c r="G46" s="42">
         <v>0.75500120080698907</v>
       </c>
-      <c r="H46" s="28"/>
-      <c r="I46" s="28"/>
-      <c r="J46" s="28" t="s">
+      <c r="H46" s="42"/>
+      <c r="I46" s="42"/>
+      <c r="J46" s="42" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A47" s="29">
+      <c r="A47" s="41">
         <v>2.2999999999999998</v>
       </c>
-      <c r="B47" s="29">
+      <c r="B47" s="41">
         <v>550</v>
       </c>
-      <c r="C47" s="29">
+      <c r="C47" s="41">
         <v>1.5</v>
       </c>
-      <c r="D47" s="7">
+      <c r="D47" s="42">
         <v>15533.485722076859</v>
       </c>
-      <c r="E47" s="7">
+      <c r="E47" s="42">
         <v>3363.0298131668801</v>
       </c>
-      <c r="F47" s="7">
+      <c r="F47" s="42">
         <v>28.376662553826502</v>
       </c>
-      <c r="G47" s="7">
+      <c r="G47" s="42">
         <v>0.78169228462799034</v>
       </c>
-      <c r="H47" s="28"/>
-      <c r="I47" s="28"/>
-      <c r="J47" s="28" t="s">
+      <c r="H47" s="42"/>
+      <c r="I47" s="42"/>
+      <c r="J47" s="42" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A48" s="29">
+      <c r="A48" s="41">
         <v>2.4</v>
       </c>
-      <c r="B48" s="29">
+      <c r="B48" s="41">
         <v>500</v>
       </c>
-      <c r="C48" s="29">
+      <c r="C48" s="41">
         <v>1.5</v>
       </c>
-      <c r="D48" s="7">
+      <c r="D48" s="42">
         <v>14959.083421784053</v>
       </c>
-      <c r="E48" s="7">
+      <c r="E48" s="42">
         <v>3254.93741638246</v>
       </c>
-      <c r="F48" s="7">
+      <c r="F48" s="42">
         <v>30.055158385509131</v>
       </c>
-      <c r="G48" s="7">
+      <c r="G48" s="42">
         <v>0.81184067264021731</v>
       </c>
-      <c r="H48" s="28"/>
-      <c r="I48" s="28"/>
-      <c r="J48" s="28" t="s">
+      <c r="H48" s="42"/>
+      <c r="I48" s="42"/>
+      <c r="J48" s="42" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="49" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A49" s="29">
+      <c r="A49" s="41">
         <v>2.5</v>
       </c>
-      <c r="B49" s="29">
+      <c r="B49" s="41">
         <v>450</v>
       </c>
-      <c r="C49" s="29">
+      <c r="C49" s="41">
         <v>1.5</v>
       </c>
-      <c r="D49" s="7">
+      <c r="D49" s="42">
         <v>14374.252301166831</v>
       </c>
-      <c r="E49" s="7">
+      <c r="E49" s="42">
         <v>3153.27929922455</v>
       </c>
-      <c r="F49" s="7">
+      <c r="F49" s="42">
         <v>32.079256576656313</v>
       </c>
-      <c r="G49" s="7">
+      <c r="G49" s="42">
         <v>0.8451290336584526</v>
       </c>
-      <c r="H49" s="28"/>
-      <c r="I49" s="28"/>
-      <c r="J49" s="28" t="s">
+      <c r="H49" s="42"/>
+      <c r="I49" s="42"/>
+      <c r="J49" s="42" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="50" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A50" s="29">
+      <c r="A50" s="39">
         <v>3.1</v>
       </c>
-      <c r="B50" s="29">
+      <c r="B50" s="39">
         <v>650</v>
       </c>
-      <c r="C50" s="29">
+      <c r="C50" s="39">
         <v>1.75</v>
       </c>
-      <c r="D50" s="7">
+      <c r="D50" s="40">
         <v>17026.825070361927</v>
       </c>
-      <c r="E50" s="7">
+      <c r="E50" s="40">
         <v>3478.9784381437985</v>
       </c>
-      <c r="F50" s="7">
+      <c r="F50" s="40">
         <v>26.153846153846153</v>
       </c>
-      <c r="G50" s="7">
+      <c r="G50" s="40">
         <v>0.71764705882352942</v>
       </c>
-      <c r="H50" s="28"/>
-      <c r="I50" s="28"/>
-      <c r="J50" s="28" t="s">
+      <c r="H50" s="40"/>
+      <c r="I50" s="40"/>
+      <c r="J50" s="40" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="51" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A51" s="29">
+      <c r="A51" s="39">
         <v>3.2</v>
       </c>
-      <c r="B51" s="29">
+      <c r="B51" s="39">
         <v>600</v>
       </c>
-      <c r="C51" s="29">
+      <c r="C51" s="39">
         <v>1.75</v>
       </c>
-      <c r="D51" s="7">
+      <c r="D51" s="40">
         <v>16564.952728166798</v>
       </c>
-      <c r="E51" s="7">
+      <c r="E51" s="40">
         <v>3396.8604949609435</v>
       </c>
-      <c r="F51" s="7">
+      <c r="F51" s="40">
         <v>27.724119108678448</v>
       </c>
-      <c r="G51" s="7">
+      <c r="G51" s="40">
         <v>0.73341675000120798</v>
       </c>
-      <c r="H51" s="28"/>
-      <c r="I51" s="28"/>
-      <c r="J51" s="28" t="s">
+      <c r="H51" s="40"/>
+      <c r="I51" s="40"/>
+      <c r="J51" s="40" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A52" s="6">
+      <c r="A52" s="39">
         <v>3.3</v>
       </c>
-      <c r="B52" s="29">
+      <c r="B52" s="39">
         <v>550</v>
       </c>
-      <c r="C52" s="29">
+      <c r="C52" s="39">
         <v>1.75</v>
       </c>
-      <c r="D52" s="7">
+      <c r="D52" s="40">
         <v>15964.320704300892</v>
       </c>
-      <c r="E52" s="7">
+      <c r="E52" s="40">
         <v>3273.7397524793669</v>
       </c>
-      <c r="F52" s="7">
+      <c r="F52" s="40">
         <v>29.16347500797994</v>
       </c>
-      <c r="G52" s="7">
+      <c r="G52" s="40">
         <v>0.76060271197957774</v>
       </c>
-      <c r="H52" s="28"/>
-      <c r="I52" s="28"/>
-      <c r="J52" s="28" t="s">
+      <c r="H52" s="40"/>
+      <c r="I52" s="40"/>
+      <c r="J52" s="40" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A53" s="6">
+      <c r="A53" s="39">
         <v>3.4</v>
       </c>
-      <c r="B53" s="29">
+      <c r="B53" s="39">
         <v>500</v>
       </c>
-      <c r="C53" s="29">
+      <c r="C53" s="39">
         <v>1.75</v>
       </c>
-      <c r="D53" s="7">
+      <c r="D53" s="40">
         <v>15342.574250694248</v>
       </c>
-      <c r="E53" s="7">
+      <c r="E53" s="40">
         <v>3150.7306586193199</v>
       </c>
-      <c r="F53" s="7">
+      <c r="F53" s="40">
         <v>30.836662860235961</v>
       </c>
-      <c r="G53" s="7">
+      <c r="G53" s="40">
         <v>0.79126590677436526</v>
       </c>
-      <c r="H53" s="28"/>
-      <c r="I53" s="28"/>
-      <c r="J53" s="28" t="s">
+      <c r="H53" s="40"/>
+      <c r="I53" s="40"/>
+      <c r="J53" s="40" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A54" s="6">
+      <c r="A54" s="39">
         <v>3.5</v>
       </c>
-      <c r="B54" s="29">
+      <c r="B54" s="39">
         <v>450</v>
       </c>
-      <c r="C54" s="29">
+      <c r="C54" s="39">
         <v>1.75</v>
       </c>
-      <c r="D54" s="7">
+      <c r="D54" s="40">
         <v>14696.0859386548</v>
       </c>
-      <c r="E54" s="7">
+      <c r="E54" s="40">
         <v>3027.9164563938398</v>
       </c>
-      <c r="F54" s="7">
+      <c r="F54" s="40">
         <v>32.809711309322054</v>
       </c>
-      <c r="G54" s="7">
+      <c r="G54" s="40">
         <v>0.82631361353698263</v>
       </c>
-      <c r="H54" s="28"/>
-      <c r="I54" s="28"/>
-      <c r="J54" s="28" t="s">
+      <c r="H54" s="40"/>
+      <c r="I54" s="40"/>
+      <c r="J54" s="40" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A55" s="6">
+      <c r="A55" s="37">
         <v>4.0999999999999996</v>
       </c>
-      <c r="B55" s="29">
+      <c r="B55" s="37">
         <v>650</v>
       </c>
-      <c r="C55" s="29">
+      <c r="C55" s="37">
         <v>2</v>
       </c>
-      <c r="D55" s="7">
+      <c r="D55" s="38">
         <v>17543.983768220623</v>
       </c>
-      <c r="E55" s="7">
+      <c r="E55" s="38">
         <v>3468.8347203783542</v>
       </c>
-      <c r="F55" s="7">
+      <c r="F55" s="38">
         <v>26.861069278214316</v>
       </c>
-      <c r="G55" s="7">
+      <c r="G55" s="38">
         <v>0.69875218200838951</v>
       </c>
-      <c r="H55" s="28"/>
-      <c r="I55" s="28"/>
-      <c r="J55" s="28" t="s">
+      <c r="H55" s="38"/>
+      <c r="I55" s="38"/>
+      <c r="J55" s="38" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="56" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A56" s="6">
+      <c r="A56" s="37">
         <v>4.2</v>
       </c>
-      <c r="B56" s="29">
+      <c r="B56" s="37">
         <v>600</v>
       </c>
-      <c r="C56" s="29">
+      <c r="C56" s="37">
         <v>2</v>
       </c>
-      <c r="D56" s="7">
+      <c r="D56" s="38">
         <v>17007.334180378537</v>
       </c>
-      <c r="E56" s="7">
+      <c r="E56" s="38">
         <v>3361.2872552344325</v>
       </c>
-      <c r="F56" s="7">
+      <c r="F56" s="38">
         <v>28.333333333333332</v>
       </c>
-      <c r="G56" s="7">
+      <c r="G56" s="38">
         <v>0.71764705882352942</v>
       </c>
-      <c r="H56" s="28"/>
-      <c r="I56" s="28"/>
-      <c r="J56" s="28" t="s">
+      <c r="H56" s="38"/>
+      <c r="I56" s="38"/>
+      <c r="J56" s="38" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="57" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A57" s="6">
+      <c r="A57" s="37">
         <v>4.3</v>
       </c>
-      <c r="B57" s="29">
+      <c r="B57" s="37">
         <v>550</v>
       </c>
-      <c r="C57" s="29">
+      <c r="C57" s="37">
         <v>2</v>
       </c>
-      <c r="D57" s="7">
+      <c r="D57" s="38">
         <v>16475.66219024115</v>
       </c>
-      <c r="E57" s="7">
+      <c r="E57" s="38">
         <v>3262.6451085876179</v>
       </c>
-      <c r="F57" s="7">
+      <c r="F57" s="38">
         <v>30.105078737406252</v>
       </c>
-      <c r="G57" s="7">
+      <c r="G57" s="38">
         <v>0.73681315951041715</v>
       </c>
-      <c r="H57" s="28"/>
-      <c r="I57" s="28"/>
-      <c r="J57" s="28" t="s">
+      <c r="H57" s="38"/>
+      <c r="I57" s="38"/>
+      <c r="J57" s="38" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="58" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A58" s="6">
+      <c r="A58" s="37">
         <v>4.4000000000000004</v>
       </c>
-      <c r="B58" s="29">
+      <c r="B58" s="37">
         <v>500</v>
       </c>
-      <c r="C58" s="29">
+      <c r="C58" s="37">
         <v>2</v>
       </c>
-      <c r="D58" s="7">
+      <c r="D58" s="38">
         <v>15785.568694069267</v>
       </c>
-      <c r="E58" s="7">
+      <c r="E58" s="38">
         <v>3119.2044574233514</v>
       </c>
-      <c r="F58" s="7">
+      <c r="F58" s="38">
         <v>31.70341220702781</v>
       </c>
-      <c r="G58" s="7">
+      <c r="G58" s="38">
         <v>0.76963324454366344</v>
       </c>
-      <c r="H58" s="28"/>
-      <c r="I58" s="28"/>
-      <c r="J58" s="28" t="s">
+      <c r="H58" s="38"/>
+      <c r="I58" s="38"/>
+      <c r="J58" s="38" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="59" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A59" s="6">
+      <c r="A59" s="37">
         <v>4.5</v>
       </c>
-      <c r="B59" s="29">
+      <c r="B59" s="37">
         <v>450</v>
       </c>
-      <c r="C59" s="29">
+      <c r="C59" s="37">
         <v>2</v>
       </c>
-      <c r="D59" s="7">
+      <c r="D59" s="38">
         <v>15098.271074105311</v>
       </c>
-      <c r="E59" s="7">
+      <c r="E59" s="38">
         <v>2984.9919544959503</v>
       </c>
-      <c r="F59" s="7">
+      <c r="F59" s="38">
         <v>33.695376889404088</v>
       </c>
-      <c r="G59" s="7">
+      <c r="G59" s="38">
         <v>0.80459438694204144</v>
       </c>
-      <c r="H59" s="28"/>
-      <c r="I59" s="28"/>
-      <c r="J59" s="28" t="s">
+      <c r="H59" s="38"/>
+      <c r="I59" s="38"/>
+      <c r="J59" s="38" t="s">
         <v>82</v>
       </c>
     </row>
@@ -2550,12 +2574,12 @@
       </c>
     </row>
     <row r="3" spans="1:6" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
       <c r="E3" s="25"/>
     </row>
     <row r="4" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -2756,12 +2780,12 @@
       <c r="B19" s="11"/>
     </row>
     <row r="21" spans="1:5" s="5" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
       <c r="E21" s="26"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -2862,10 +2886,10 @@
       </c>
     </row>
     <row r="32" spans="1:5" s="10" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A32" s="32" t="s">
+      <c r="A32" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="32"/>
+      <c r="B32" s="30"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -2892,18 +2916,18 @@
       </c>
     </row>
     <row r="37" spans="1:11" s="9" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A37" s="33" t="s">
+      <c r="A37" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="33"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
     </row>
     <row r="38" spans="1:11" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>
@@ -2913,17 +2937,17 @@
       <c r="C38" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="34" t="s">
+      <c r="D38" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="E38" s="35"/>
-      <c r="F38" s="36" t="s">
+      <c r="E38" s="33"/>
+      <c r="F38" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="G38" s="37"/>
-      <c r="H38" s="37"/>
-      <c r="I38" s="37"/>
-      <c r="J38" s="38"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="35"/>
+      <c r="J38" s="36"/>
       <c r="K38" s="2"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
@@ -3097,12 +3121,12 @@
       </c>
     </row>
     <row r="3" spans="1:6" s="3" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A3" s="30" t="s">
+      <c r="A3" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B3" s="30"/>
-      <c r="C3" s="30"/>
-      <c r="D3" s="30"/>
+      <c r="B3" s="28"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
       <c r="E3" s="25"/>
     </row>
     <row r="4" spans="1:6" s="3" customFormat="1" x14ac:dyDescent="0.3">
@@ -3303,12 +3327,12 @@
       <c r="B19" s="11"/>
     </row>
     <row r="21" spans="1:5" s="5" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A21" s="31" t="s">
+      <c r="A21" s="29" t="s">
         <v>28</v>
       </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="31"/>
-      <c r="D21" s="31"/>
+      <c r="B21" s="29"/>
+      <c r="C21" s="29"/>
+      <c r="D21" s="29"/>
       <c r="E21" s="26"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.3">
@@ -3390,10 +3414,10 @@
       <c r="A30" s="2"/>
     </row>
     <row r="32" spans="1:5" s="10" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A32" s="32" t="s">
+      <c r="A32" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="B32" s="32"/>
+      <c r="B32" s="30"/>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
@@ -3420,18 +3444,18 @@
       </c>
     </row>
     <row r="37" spans="1:11" s="9" customFormat="1" ht="21" x14ac:dyDescent="0.4">
-      <c r="A37" s="33" t="s">
+      <c r="A37" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="B37" s="33"/>
-      <c r="C37" s="33"/>
-      <c r="D37" s="33"/>
-      <c r="E37" s="33"/>
-      <c r="F37" s="33"/>
-      <c r="G37" s="33"/>
-      <c r="H37" s="33"/>
-      <c r="I37" s="33"/>
-      <c r="J37" s="33"/>
+      <c r="B37" s="31"/>
+      <c r="C37" s="31"/>
+      <c r="D37" s="31"/>
+      <c r="E37" s="31"/>
+      <c r="F37" s="31"/>
+      <c r="G37" s="31"/>
+      <c r="H37" s="31"/>
+      <c r="I37" s="31"/>
+      <c r="J37" s="31"/>
     </row>
     <row r="38" spans="1:11" ht="58.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A38" s="8"/>
@@ -3441,17 +3465,17 @@
       <c r="C38" s="12" t="s">
         <v>26</v>
       </c>
-      <c r="D38" s="34" t="s">
+      <c r="D38" s="32" t="s">
         <v>60</v>
       </c>
-      <c r="E38" s="35"/>
-      <c r="F38" s="36" t="s">
+      <c r="E38" s="33"/>
+      <c r="F38" s="34" t="s">
         <v>61</v>
       </c>
-      <c r="G38" s="37"/>
-      <c r="H38" s="37"/>
-      <c r="I38" s="37"/>
-      <c r="J38" s="38"/>
+      <c r="G38" s="35"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="35"/>
+      <c r="J38" s="36"/>
       <c r="K38" s="2"/>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.3">
